--- a/outputs/evaluation/requirement/validation/gemini-3-1-flash-lite/CF_M04/first/CF_M04_req_eval.xlsx
+++ b/outputs/evaluation/requirement/validation/gemini-3-1-flash-lite/CF_M04/first/CF_M04_req_eval.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -546,6 +551,9 @@
         <v>0.9737</v>
       </c>
       <c r="D13" t="n">
+        <v>0.9737</v>
+      </c>
+      <c r="E13" t="n">
         <v>0.9804</v>
       </c>
     </row>
@@ -755,10 +763,6 @@
           <t>The system shall display a Home screen with relevant business information for authenticated users.</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>FR</t>
@@ -773,10 +777,6 @@
 of my business</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -807,10 +807,6 @@
           <t>The system shall allow delegated users to log in using their email or phone number.</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>FR</t>
@@ -825,10 +821,6 @@
 phone number</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -859,10 +851,6 @@
           <t>The system shall allow users to view images and videos associated with a review.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>FR</t>
@@ -876,10 +864,6 @@
           <t xml:space="preserve"> I want to be able to see images and videos associated with a review</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -910,10 +894,6 @@
           <t>The system shall allow users to access the application menu from different screens.</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>FR</t>
@@ -927,10 +907,6 @@
           <t>I want to be able to access the application menu from different screens</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -966,9 +942,6 @@
           <t>C_03</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>QR</t>
@@ -992,8 +965,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1024,14 +995,11 @@
           <t>Access to functionalities requires valid authentication and unauthorized access is not permitted.</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>R_35</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1045,14 +1013,11 @@
           <t>Access to features requires valid authentication and is not allows unauthorized access.</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>CF_M04_R35</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1083,14 +1048,11 @@
           <t>The system must show loading and error states when necessary.</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>R_07</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1104,14 +1066,11 @@
           <t>The system must display loading and error statuses when necessary.</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>CF_M04_R07</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1142,14 +1101,11 @@
           <t>Multimedia content must be displayed below the review text.</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>R_20</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1163,14 +1119,11 @@
           <t>Multimedia content should be displayed below the review text.</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>CF_M04_R20</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1201,14 +1154,11 @@
           <t>The suggestion must be generated automatically upon opening the response modal.</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>R_12</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1222,14 +1172,11 @@
           <t>The suggestion should be generated automatically when opening the response modal.</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>CF_M04_R12</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1260,14 +1207,11 @@
           <t>Images must be navigable via horizontal scroll.</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>R_20</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1281,14 +1225,11 @@
           <t>The images must be navigable via horizontal scrolling.</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>CF_M04_R20</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1324,9 +1265,6 @@
           <t>C_01</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1350,8 +1288,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1387,9 +1323,6 @@
           <t>C_05</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1413,8 +1346,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1445,14 +1376,11 @@
           <t>If the user does not have Cintia credits, they will be notified and provided with a button to purchase them.</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>R_12</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1467,14 +1395,11 @@
 buy them.</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>CF_M04_R12</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1505,14 +1430,11 @@
           <t>The application is displayed and functions correctly on emulators and physical Android and iOS devices.</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>R_31</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1526,14 +1448,11 @@
           <t>The application displays and works correctly on emulators and physical Android and iOS devices.</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>CF_M04_R31</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1564,14 +1483,11 @@
           <t>Upon clicking an image or video, it must be displayed in full screen.</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>R_20</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1585,14 +1501,11 @@
           <t>When clicking an image or video, it must be displayed in full screen.</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>CF_M04_R20</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1623,14 +1536,11 @@
           <t>If Cintia is active, the system must show a response suggestion.</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>R_12</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1644,14 +1554,11 @@
           <t>If Cintia is active, the system must display a response suggestion.</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>CF_M04_R12</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1682,14 +1589,11 @@
           <t>The menu behavior must be consistent with the rest of the application.</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>R_25</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1703,14 +1607,11 @@
           <t>The menu's behavior must be consistent with the rest of the application.</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>CF_M04_R25</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1741,14 +1642,11 @@
           <t>Main calls to the backend return a response in a time perceived as acceptable by the user.</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>R_33</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1762,14 +1660,11 @@
           <t>The main calls to the backend return a response in a time perceived as acceptable by the user.</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>CF_M04_R33</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1800,14 +1695,11 @@
           <t>Access to the menu must be performed via the user's profile image.</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>R_25</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1821,14 +1713,11 @@
           <t>Access to the menu must be done through the user's profile image.</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>CF_M04_R25</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1859,14 +1748,11 @@
           <t>The system must display images and videos associated with a review.</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>R_20</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1880,14 +1766,11 @@
           <t>The system must display the images and videos associated with a review.</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>CF_M04_R20</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1918,14 +1801,11 @@
           <t>Main functionalities can be used without errors after a first use; no external instructions are required to complete basic actions.</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>R_29</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1939,14 +1819,11 @@
           <t>The main functionalities can be used without errors after a first use; no external instructions are required to complete basic actions.</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>CF_M04_R29</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1977,14 +1854,11 @@
           <t>The Home screen must show several independent informative widgets.</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>R_07</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1998,14 +1872,11 @@
           <t>The Home screen must display several independent informative widgets.</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>CF_M04_R07</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2036,14 +1907,11 @@
           <t>The code follows a clear architecture and is reviewable via PRs without difficulty.</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>R_37</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2057,14 +1925,11 @@
           <t>The code follows a clear architecture and is reviewable through PRs without difficulty.</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>CF_M04_R37</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2095,14 +1960,11 @@
           <t>If the code is correct, the user must log in successfully.</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2116,14 +1978,11 @@
           <t>If the code is correct, the user must log in successfully.</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>CF_M04_R01</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2154,14 +2013,11 @@
           <t>The system must display the response progressively (typing effect).</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>R_12</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2175,14 +2031,11 @@
           <t>The system must display the response progressively (typing effect).</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>CF_M04_R12</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2213,14 +2066,11 @@
           <t>The system must allow entering an email address or a phone number.</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2234,14 +2084,11 @@
           <t>The system must allow entering an email address or a phone number.</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>CF_M04_R01</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2272,14 +2119,11 @@
           <t>Each widget must load its data autonomously.</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>R_07</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2293,14 +2137,11 @@
           <t>Each widget must load its data autonomously.</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>CF_M04_R07</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2331,14 +2172,11 @@
           <t>The user must be able to enter the received OTP code.</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2352,14 +2190,11 @@
           <t>The user must be able to enter the received OTP code.</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>CF_M04_R01</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2395,9 +2230,6 @@
           <t>C_04</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>QR</t>
@@ -2421,8 +2253,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2458,9 +2288,6 @@
           <t>C_02</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>QR</t>
@@ -2484,8 +2311,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2516,14 +2341,11 @@
           <t>The user must be able to edit or replace the suggested response.</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>R_12</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2537,14 +2359,11 @@
           <t>The user must be able to edit or replace the suggested response.</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>CF_M04_R12</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2575,14 +2394,11 @@
           <t>The visual layout must be consistent with the established design.</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>R_07</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2596,14 +2412,11 @@
           <t>The visual layout must be consistent with the established design.</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>CF_M04_R07</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2634,14 +2447,11 @@
           <t>The system must detect if the user has the Cintia functionality activated.</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>R_12</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2655,14 +2465,11 @@
           <t>The system must detect if the user has the Cintia functionality activated.</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>CF_M04_R12</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2693,14 +2500,11 @@
           <t>The menu must be accessible from more than one screen.</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>R_25</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2714,14 +2518,11 @@
           <t>The menu must be accessible from more than one screen.</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>CF_M04_R25</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2752,14 +2553,11 @@
           <t>If the user does not see a response despite having credits, a button will appear to request the response.</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>R_12</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2773,14 +2571,11 @@
           <t>If the user does not see a response despite having credits, a button will appear to request the response.</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>CF_M04_R12</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2811,14 +2606,11 @@
           <t>The system must handle authentication errors and incorrect codes.</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2832,14 +2624,11 @@
           <t>The system must handle authentication errors and incorrect codes.</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>CF_M04_R01</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2870,14 +2659,11 @@
           <t>The system must send an OTP code to the indicated address or number.</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2891,14 +2677,11 @@
           <t>The system must send an OTP code to the indicated address or number.</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>CF_M04_R01</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
